--- a/Analisis_Usabilidad_Final.xlsx
+++ b/Analisis_Usabilidad_Final.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Usabilidad Baja" sheetId="3" r:id="rId3"/>
     <sheet name="Monto por User Team" sheetId="4" r:id="rId4"/>
     <sheet name="Resumen Niveles" sheetId="5" r:id="rId5"/>
+    <sheet name="% Uso por Team" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Análisis Detallado'!$A$4:$AJ$90</definedName>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1245" uniqueCount="268">
   <si>
     <t>Nombre</t>
   </si>
@@ -743,6 +744,9 @@
     <t>1.Muy Alto</t>
   </si>
   <si>
+    <t>Reciente</t>
+  </si>
+  <si>
     <t>Revisar</t>
   </si>
   <si>
@@ -752,6 +756,9 @@
     <t>Mantener</t>
   </si>
   <si>
+    <t>Seguimiento (reciente)</t>
+  </si>
+  <si>
     <t>Upgrade a Premium | Consolidado de 2 asignaciones (upgrade). Licencia vigente: Team plan - Premium - Anual. Historial: Team plan - Premium - Anual + Team plan - Standard - Anual.</t>
   </si>
   <si>
@@ -788,6 +795,12 @@
     <t>Volumetría: crecimiento de licencias asignadas en el tiempo</t>
   </si>
   <si>
+    <t>Última conexión</t>
+  </si>
+  <si>
+    <t>Días activos</t>
+  </si>
+  <si>
     <t>Usuarios con usabilidad baja (Nivel Bajo / Nulo)</t>
   </si>
   <si>
@@ -807,6 +820,12 @@
   </si>
   <si>
     <t>Distribución de usuarios por Nivel de uso</t>
+  </si>
+  <si>
+    <t>Días activos promedio</t>
+  </si>
+  <si>
+    <t>Promedio de % de uso por User Team</t>
   </si>
 </sst>
 </file>
@@ -1496,9 +1515,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Resumen Niveles'!$A$4:$A$8</c:f>
+              <c:f>'Resumen Niveles'!$A$4:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>1.Muy Alto</c:v>
                 </c:pt>
@@ -1514,15 +1533,18 @@
                 <c:pt idx="4">
                   <c:v>5.Nulo</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>Reciente</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Resumen Niveles'!$B$4:$B$8</c:f>
+              <c:f>'Resumen Niveles'!$B$4:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>7</c:v>
                 </c:pt>
@@ -1536,7 +1558,10 @@
                   <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>33</c:v>
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1568,6 +1593,175 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>% de uso promedio por User Team</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>% de uso promedio</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4338CA"/>
+            </a:solidFill>
+          </c:spPr>
+          <c:dLbls>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'% Uso por Team'!$A$4:$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>IT </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Ops - Cyber</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Finanzas</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ops - Preventa</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Compras</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Ops - DX</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Dirección</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Ops - Cuesto</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>RR. HH.</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Ops - Nube</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Ops - Implement</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'% Uso por Team'!$C$4:$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>107.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>96.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>81.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>69.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>47.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>37.3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27.6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50040001"/>
+        <c:axId val="50040002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50040001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50040002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50040002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50040001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1669,6 +1863,41 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2005,12 +2234,12 @@
   <sheetData>
     <row r="1" spans="1:36">
       <c r="A1" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:36">
       <c r="A2" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:36">
@@ -2227,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AI5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:36">
@@ -2334,7 +2563,7 @@
         <v>2</v>
       </c>
       <c r="AI6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:36">
@@ -2441,7 +2670,7 @@
         <v>4</v>
       </c>
       <c r="AI7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:36">
@@ -2548,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="AI8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:36">
@@ -2655,7 +2884,7 @@
         <v>2</v>
       </c>
       <c r="AI9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:36">
@@ -2762,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="AI10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:36">
@@ -2869,7 +3098,7 @@
         <v>4</v>
       </c>
       <c r="AI11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:36">
@@ -2976,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="AI12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" spans="1:36">
@@ -3083,7 +3312,7 @@
         <v>3</v>
       </c>
       <c r="AI13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:36">
@@ -3190,7 +3419,7 @@
         <v>3</v>
       </c>
       <c r="AI14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:36">
@@ -3297,7 +3526,7 @@
         <v>2</v>
       </c>
       <c r="AI15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:36">
@@ -3404,10 +3633,10 @@
         <v>4</v>
       </c>
       <c r="AI16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AJ16" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:36">
@@ -3511,10 +3740,10 @@
         <v>0</v>
       </c>
       <c r="AI17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ17" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:36">
@@ -3621,7 +3850,7 @@
         <v>2</v>
       </c>
       <c r="AI18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:36">
@@ -3728,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="AI19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:36">
@@ -3835,7 +4064,7 @@
         <v>3</v>
       </c>
       <c r="AI20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" spans="1:36">
@@ -3942,7 +4171,7 @@
         <v>3</v>
       </c>
       <c r="AI21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:36">
@@ -4049,7 +4278,7 @@
         <v>2</v>
       </c>
       <c r="AI22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" spans="1:36">
@@ -4156,7 +4385,7 @@
         <v>2</v>
       </c>
       <c r="AI23" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24" spans="1:36">
@@ -4263,7 +4492,7 @@
         <v>2</v>
       </c>
       <c r="AI24" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:36">
@@ -4370,7 +4599,7 @@
         <v>2</v>
       </c>
       <c r="AI25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:36">
@@ -4477,7 +4706,7 @@
         <v>3</v>
       </c>
       <c r="AI26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="27" spans="1:36">
@@ -4584,7 +4813,7 @@
         <v>1</v>
       </c>
       <c r="AI27" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:36">
@@ -4691,7 +4920,7 @@
         <v>3</v>
       </c>
       <c r="AI28" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" spans="1:36">
@@ -4798,7 +5027,7 @@
         <v>3</v>
       </c>
       <c r="AI29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" spans="1:36">
@@ -4905,7 +5134,7 @@
         <v>1</v>
       </c>
       <c r="AI30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:36">
@@ -5012,7 +5241,7 @@
         <v>3</v>
       </c>
       <c r="AI31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" spans="1:36">
@@ -5119,7 +5348,7 @@
         <v>1</v>
       </c>
       <c r="AI32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" spans="1:36">
@@ -5226,7 +5455,7 @@
         <v>2</v>
       </c>
       <c r="AI33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:36">
@@ -5333,7 +5562,7 @@
         <v>3</v>
       </c>
       <c r="AI34" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:36">
@@ -5437,10 +5666,10 @@
         <v>0</v>
       </c>
       <c r="AI35" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ35" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" spans="1:36">
@@ -5547,7 +5776,7 @@
         <v>1</v>
       </c>
       <c r="AI36" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37" spans="1:36">
@@ -5654,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="AI37" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:36">
@@ -5761,7 +5990,7 @@
         <v>2</v>
       </c>
       <c r="AI38" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="39" spans="1:36">
@@ -5868,7 +6097,7 @@
         <v>3</v>
       </c>
       <c r="AI39" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:36">
@@ -5975,7 +6204,7 @@
         <v>2</v>
       </c>
       <c r="AI40" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41" spans="1:36">
@@ -6082,7 +6311,7 @@
         <v>4</v>
       </c>
       <c r="AI41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="42" spans="1:36">
@@ -6189,7 +6418,7 @@
         <v>4</v>
       </c>
       <c r="AI42" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="43" spans="1:36">
@@ -6296,7 +6525,7 @@
         <v>3</v>
       </c>
       <c r="AI43" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="44" spans="1:36">
@@ -6403,7 +6632,7 @@
         <v>1</v>
       </c>
       <c r="AI44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="45" spans="1:36">
@@ -6510,7 +6739,7 @@
         <v>3</v>
       </c>
       <c r="AI45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="46" spans="1:36">
@@ -6617,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="AI46" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="47" spans="1:36">
@@ -6724,7 +6953,7 @@
         <v>5</v>
       </c>
       <c r="AI47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="48" spans="1:36">
@@ -6831,7 +7060,7 @@
         <v>2</v>
       </c>
       <c r="AI48" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:36">
@@ -6938,7 +7167,7 @@
         <v>2</v>
       </c>
       <c r="AI49" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="50" spans="1:36">
@@ -7042,7 +7271,7 @@
         <v>0</v>
       </c>
       <c r="AI50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="51" spans="1:36">
@@ -7149,7 +7378,7 @@
         <v>4</v>
       </c>
       <c r="AI51" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52" spans="1:36">
@@ -7256,7 +7485,7 @@
         <v>3</v>
       </c>
       <c r="AI52" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="53" spans="1:36">
@@ -7363,7 +7592,7 @@
         <v>3</v>
       </c>
       <c r="AI53" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:36">
@@ -7470,7 +7699,7 @@
         <v>3</v>
       </c>
       <c r="AI54" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="55" spans="1:36">
@@ -7577,7 +7806,7 @@
         <v>3</v>
       </c>
       <c r="AI55" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="56" spans="1:36">
@@ -7681,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="AI56" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="57" spans="1:36">
@@ -7788,7 +8017,7 @@
         <v>0</v>
       </c>
       <c r="AI57" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:36">
@@ -7895,7 +8124,7 @@
         <v>2</v>
       </c>
       <c r="AI58" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="59" spans="1:36">
@@ -8002,7 +8231,7 @@
         <v>3</v>
       </c>
       <c r="AI59" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="60" spans="1:36">
@@ -8109,7 +8338,7 @@
         <v>2</v>
       </c>
       <c r="AI60" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="61" spans="1:36">
@@ -8216,7 +8445,7 @@
         <v>3</v>
       </c>
       <c r="AI61" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" spans="1:36">
@@ -8323,7 +8552,7 @@
         <v>1</v>
       </c>
       <c r="AI62" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="63" spans="1:36">
@@ -8430,7 +8659,7 @@
         <v>1</v>
       </c>
       <c r="AI63" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="64" spans="1:36">
@@ -8537,10 +8766,10 @@
         <v>2</v>
       </c>
       <c r="AI64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AJ64" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="65" spans="1:35">
@@ -8638,13 +8867,13 @@
         <v>0</v>
       </c>
       <c r="AG65" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH65">
         <v>0</v>
       </c>
       <c r="AI65" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" spans="1:35">
@@ -8742,13 +8971,13 @@
         <v>0</v>
       </c>
       <c r="AG66" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH66">
         <v>0</v>
       </c>
       <c r="AI66" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="67" spans="1:35">
@@ -8846,13 +9075,13 @@
         <v>0</v>
       </c>
       <c r="AG67" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH67">
         <v>0</v>
       </c>
       <c r="AI67" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" spans="1:35">
@@ -8950,13 +9179,13 @@
         <v>0</v>
       </c>
       <c r="AG68" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH68">
         <v>0</v>
       </c>
       <c r="AI68" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69" spans="1:35">
@@ -9054,13 +9283,13 @@
         <v>0</v>
       </c>
       <c r="AG69" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH69">
         <v>0</v>
       </c>
       <c r="AI69" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="70" spans="1:35">
@@ -9167,7 +9396,7 @@
         <v>1</v>
       </c>
       <c r="AI70" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" spans="1:35">
@@ -9265,13 +9494,13 @@
         <v>0</v>
       </c>
       <c r="AG71" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH71">
         <v>0</v>
       </c>
       <c r="AI71" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:35">
@@ -9369,13 +9598,13 @@
         <v>0</v>
       </c>
       <c r="AG72" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH72">
         <v>0</v>
       </c>
       <c r="AI72" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" spans="1:35">
@@ -9473,13 +9702,13 @@
         <v>0</v>
       </c>
       <c r="AG73" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH73">
         <v>0</v>
       </c>
       <c r="AI73" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:35">
@@ -9577,13 +9806,13 @@
         <v>0</v>
       </c>
       <c r="AG74" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH74">
         <v>0</v>
       </c>
       <c r="AI74" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" spans="1:35">
@@ -9681,13 +9910,13 @@
         <v>0</v>
       </c>
       <c r="AG75" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH75">
         <v>0</v>
       </c>
       <c r="AI75" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:35">
@@ -9785,13 +10014,13 @@
         <v>0</v>
       </c>
       <c r="AG76" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH76">
         <v>0</v>
       </c>
       <c r="AI76" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="77" spans="1:35">
@@ -9889,13 +10118,13 @@
         <v>0</v>
       </c>
       <c r="AG77" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH77">
         <v>0</v>
       </c>
       <c r="AI77" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="78" spans="1:35">
@@ -9993,13 +10222,13 @@
         <v>0</v>
       </c>
       <c r="AG78" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH78">
         <v>0</v>
       </c>
       <c r="AI78" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="79" spans="1:35">
@@ -10097,13 +10326,13 @@
         <v>0</v>
       </c>
       <c r="AG79" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH79">
         <v>0</v>
       </c>
       <c r="AI79" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="80" spans="1:35">
@@ -10201,13 +10430,13 @@
         <v>0</v>
       </c>
       <c r="AG80" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH80">
         <v>0</v>
       </c>
       <c r="AI80" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="81" spans="1:35">
@@ -10305,13 +10534,13 @@
         <v>0</v>
       </c>
       <c r="AG81" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH81">
         <v>0</v>
       </c>
       <c r="AI81" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="82" spans="1:35">
@@ -10409,13 +10638,13 @@
         <v>0</v>
       </c>
       <c r="AG82" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH82">
         <v>0</v>
       </c>
       <c r="AI82" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:35">
@@ -10513,13 +10742,13 @@
         <v>0</v>
       </c>
       <c r="AG83" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH83">
         <v>0</v>
       </c>
       <c r="AI83" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="84" spans="1:35">
@@ -10617,13 +10846,13 @@
         <v>0</v>
       </c>
       <c r="AG84" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH84">
         <v>0</v>
       </c>
       <c r="AI84" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="85" spans="1:35">
@@ -10721,13 +10950,13 @@
         <v>0</v>
       </c>
       <c r="AG85" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH85">
         <v>0</v>
       </c>
       <c r="AI85" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:35">
@@ -10825,13 +11054,13 @@
         <v>0</v>
       </c>
       <c r="AG86" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH86">
         <v>0</v>
       </c>
       <c r="AI86" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:35">
@@ -10929,13 +11158,13 @@
         <v>0</v>
       </c>
       <c r="AG87" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH87">
         <v>0</v>
       </c>
       <c r="AI87" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="88" spans="1:35">
@@ -11033,13 +11262,13 @@
         <v>0</v>
       </c>
       <c r="AG88" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH88">
         <v>0</v>
       </c>
       <c r="AI88" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:35">
@@ -11137,13 +11366,13 @@
         <v>0</v>
       </c>
       <c r="AG89" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH89">
         <v>0</v>
       </c>
       <c r="AI89" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" spans="1:35">
@@ -11241,13 +11470,13 @@
         <v>0</v>
       </c>
       <c r="AG90" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AH90">
         <v>0</v>
       </c>
       <c r="AI90" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -11278,24 +11507,24 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -11527,29 +11756,31 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="6" width="16.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="1" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="9" width="16.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>32</v>
@@ -11558,182 +11789,254 @@
         <v>31</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>223</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>216</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
         <v>236</v>
       </c>
       <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>88</v>
-      </c>
-      <c r="G4" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>1.6</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46157</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>63</v>
+      </c>
+      <c r="I4">
+        <v>86</v>
+      </c>
+      <c r="J4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>223</v>
       </c>
       <c r="B5" t="s">
-        <v>147</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>216</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
         <v>236</v>
       </c>
       <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>47</v>
-      </c>
-      <c r="G5" t="s">
+        <v>9.5</v>
+      </c>
+      <c r="F5" s="6">
+        <v>46211</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>63</v>
+      </c>
+      <c r="I5">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E6">
+        <v>28.6</v>
+      </c>
+      <c r="F6" s="6">
+        <v>46233</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6">
+        <v>63</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D6" t="s">
-        <v>236</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>47</v>
-      </c>
-      <c r="G6" t="s">
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E7">
+        <v>30.2</v>
+      </c>
+      <c r="F7" s="6">
+        <v>46239</v>
+      </c>
+      <c r="G7">
+        <v>19</v>
+      </c>
+      <c r="H7">
+        <v>63</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8">
+        <v>33.3</v>
+      </c>
+      <c r="F8" s="6">
+        <v>46241</v>
+      </c>
+      <c r="G8">
+        <v>21</v>
+      </c>
+      <c r="H8">
+        <v>63</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" t="s">
+        <v>235</v>
+      </c>
+      <c r="E9">
+        <v>34.9</v>
+      </c>
+      <c r="F9" s="6">
+        <v>46241</v>
+      </c>
+      <c r="G9">
+        <v>22</v>
+      </c>
+      <c r="H9">
+        <v>63</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" t="s">
+        <v>235</v>
+      </c>
+      <c r="E10">
+        <v>36.5</v>
+      </c>
+      <c r="F10" s="6">
+        <v>46240</v>
+      </c>
+      <c r="G10">
+        <v>23</v>
+      </c>
+      <c r="H10">
+        <v>63</v>
+      </c>
+      <c r="I10">
+        <v>3</v>
+      </c>
+      <c r="J10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" t="s">
         <v>82</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C11" t="s">
         <v>168</v>
-      </c>
-      <c r="C7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D7" t="s">
-        <v>236</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D8" t="s">
-        <v>236</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C9" t="s">
-        <v>221</v>
-      </c>
-      <c r="D9" t="s">
-        <v>236</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>3</v>
-      </c>
-      <c r="G9" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B10" t="s">
-        <v>179</v>
-      </c>
-      <c r="C10" t="s">
-        <v>222</v>
-      </c>
-      <c r="D10" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B11" t="s">
-        <v>180</v>
-      </c>
-      <c r="C11" t="s">
-        <v>222</v>
       </c>
       <c r="D11" t="s">
         <v>236</v>
@@ -11741,160 +12044,220 @@
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>21</v>
+      </c>
+      <c r="I11">
+        <v>30</v>
+      </c>
+      <c r="J11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="B12" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>222</v>
+        <v>170</v>
       </c>
       <c r="D12" t="s">
         <v>236</v>
       </c>
       <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
+        <v>9.5</v>
+      </c>
+      <c r="F12" s="6">
+        <v>46230</v>
+      </c>
+      <c r="G12">
         <v>2</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12">
+        <v>21</v>
+      </c>
+      <c r="I12">
+        <v>13</v>
+      </c>
+      <c r="J12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13">
+        <v>14.3</v>
+      </c>
+      <c r="F13" s="6">
+        <v>46243</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13">
+        <v>21</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" t="s">
-        <v>183</v>
-      </c>
-      <c r="C13" t="s">
-        <v>222</v>
-      </c>
-      <c r="D13" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" t="s">
+        <v>235</v>
+      </c>
+      <c r="E14">
+        <v>14.3</v>
+      </c>
+      <c r="F14" s="6">
+        <v>46240</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14">
+        <v>21</v>
+      </c>
+      <c r="I14">
+        <v>3</v>
+      </c>
+      <c r="J14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" t="s">
+        <v>235</v>
+      </c>
+      <c r="E15">
+        <v>14.3</v>
+      </c>
+      <c r="F15" s="6">
+        <v>46241</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>21</v>
+      </c>
+      <c r="I15">
         <v>2</v>
       </c>
-      <c r="G13" t="s">
+      <c r="J15" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" t="s">
-        <v>184</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" t="s">
+        <v>175</v>
+      </c>
+      <c r="D16" t="s">
+        <v>235</v>
+      </c>
+      <c r="E16">
+        <v>23.8</v>
+      </c>
+      <c r="F16" s="6">
+        <v>46238</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16">
+        <v>21</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" t="s">
+        <v>235</v>
+      </c>
+      <c r="E17">
+        <v>33.3</v>
+      </c>
+      <c r="F17" s="6">
+        <v>46224</v>
+      </c>
+      <c r="G17">
+        <v>7</v>
+      </c>
+      <c r="H17">
+        <v>21</v>
+      </c>
+      <c r="I17">
+        <v>19</v>
+      </c>
+      <c r="J17" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
         <v>216</v>
       </c>
-      <c r="D14" t="s">
-        <v>236</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" t="s">
-        <v>185</v>
-      </c>
-      <c r="C15" t="s">
-        <v>216</v>
-      </c>
-      <c r="D15" t="s">
-        <v>236</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" t="s">
-        <v>186</v>
-      </c>
-      <c r="C16" t="s">
-        <v>216</v>
-      </c>
-      <c r="D16" t="s">
-        <v>236</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" t="s">
-        <v>187</v>
-      </c>
-      <c r="C17" t="s">
-        <v>216</v>
-      </c>
-      <c r="D17" t="s">
-        <v>236</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>102</v>
-      </c>
       <c r="B18" t="s">
-        <v>188</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>216</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
         <v>236</v>
@@ -11902,22 +12265,28 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>63</v>
+      </c>
+      <c r="I18">
+        <v>88</v>
+      </c>
+      <c r="J18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>103</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s">
-        <v>189</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>216</v>
+        <v>147</v>
       </c>
       <c r="D19" t="s">
         <v>236</v>
@@ -11925,22 +12294,28 @@
       <c r="E19">
         <v>0</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>34</v>
+      </c>
+      <c r="I19">
+        <v>47</v>
+      </c>
+      <c r="J19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>104</v>
+        <v>216</v>
       </c>
       <c r="B20" t="s">
-        <v>190</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="D20" t="s">
         <v>236</v>
@@ -11948,793 +12323,305 @@
       <c r="E20">
         <v>0</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>34</v>
+      </c>
+      <c r="I20">
+        <v>47</v>
+      </c>
+      <c r="J20" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s">
-        <v>191</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>216</v>
+        <v>158</v>
       </c>
       <c r="D21" t="s">
         <v>236</v>
       </c>
       <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21" t="s">
+        <v>2.9</v>
+      </c>
+      <c r="F21" s="6">
+        <v>46196</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>34</v>
+      </c>
+      <c r="I21">
+        <v>47</v>
+      </c>
+      <c r="J21" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>216</v>
+      </c>
+      <c r="B22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s">
+        <v>156</v>
+      </c>
+      <c r="D22" t="s">
+        <v>235</v>
+      </c>
+      <c r="E22">
+        <v>11.8</v>
+      </c>
+      <c r="F22" s="6">
+        <v>46231</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>34</v>
+      </c>
+      <c r="I22">
+        <v>12</v>
+      </c>
+      <c r="J22" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>106</v>
-      </c>
-      <c r="B22" t="s">
-        <v>192</v>
-      </c>
-      <c r="C22" t="s">
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
         <v>216</v>
       </c>
-      <c r="D22" t="s">
-        <v>236</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>142</v>
+      </c>
+      <c r="D23" t="s">
+        <v>235</v>
+      </c>
+      <c r="E23">
+        <v>16.7</v>
+      </c>
+      <c r="F23" s="6">
+        <v>46240</v>
+      </c>
+      <c r="G23">
+        <v>8</v>
+      </c>
+      <c r="H23">
+        <v>48</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
+      </c>
+      <c r="J23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>107</v>
-      </c>
-      <c r="B23" t="s">
-        <v>193</v>
-      </c>
-      <c r="C23" t="s">
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
         <v>216</v>
       </c>
-      <c r="D23" t="s">
-        <v>236</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" t="s">
+        <v>235</v>
+      </c>
+      <c r="E24">
+        <v>23.5</v>
+      </c>
+      <c r="F24" s="6">
+        <v>46219</v>
+      </c>
+      <c r="G24">
+        <v>8</v>
+      </c>
+      <c r="H24">
+        <v>34</v>
+      </c>
+      <c r="I24">
+        <v>24</v>
+      </c>
+      <c r="J24" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C24" t="s">
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
         <v>216</v>
       </c>
-      <c r="D24" t="s">
-        <v>236</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="B25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" t="s">
+        <v>235</v>
+      </c>
+      <c r="E25">
+        <v>32.4</v>
+      </c>
+      <c r="F25" s="6">
+        <v>46237</v>
+      </c>
+      <c r="G25">
+        <v>11</v>
+      </c>
+      <c r="H25">
+        <v>34</v>
+      </c>
+      <c r="I25">
+        <v>6</v>
+      </c>
+      <c r="J25" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>109</v>
-      </c>
-      <c r="B25" t="s">
-        <v>195</v>
-      </c>
-      <c r="C25" t="s">
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
         <v>216</v>
       </c>
-      <c r="D25" t="s">
-        <v>236</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="B26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E26">
+        <v>41.7</v>
+      </c>
+      <c r="F26" s="6">
+        <v>46240</v>
+      </c>
+      <c r="G26">
+        <v>20</v>
+      </c>
+      <c r="H26">
+        <v>48</v>
+      </c>
+      <c r="I26">
+        <v>3</v>
+      </c>
+      <c r="J26" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B26" t="s">
-        <v>196</v>
-      </c>
-      <c r="C26" t="s">
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
         <v>216</v>
       </c>
-      <c r="D26" t="s">
-        <v>236</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" t="s">
+        <v>235</v>
+      </c>
+      <c r="E27">
+        <v>43.8</v>
+      </c>
+      <c r="F27" s="6">
+        <v>46240</v>
+      </c>
+      <c r="G27">
+        <v>21</v>
+      </c>
+      <c r="H27">
+        <v>48</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" t="s">
-        <v>111</v>
-      </c>
-      <c r="B27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C27" t="s">
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
         <v>216</v>
       </c>
-      <c r="D27" t="s">
-        <v>236</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" t="s">
+        <v>235</v>
+      </c>
+      <c r="E28">
+        <v>43.8</v>
+      </c>
+      <c r="F28" s="6">
+        <v>46237</v>
+      </c>
+      <c r="G28">
+        <v>21</v>
+      </c>
+      <c r="H28">
+        <v>48</v>
+      </c>
+      <c r="I28">
+        <v>6</v>
+      </c>
+      <c r="J28" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" t="s">
-        <v>198</v>
-      </c>
-      <c r="C28" t="s">
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
         <v>216</v>
       </c>
-      <c r="D28" t="s">
-        <v>236</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28" t="s">
+      <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
+        <v>157</v>
+      </c>
+      <c r="D29" t="s">
+        <v>235</v>
+      </c>
+      <c r="E29">
+        <v>44.1</v>
+      </c>
+      <c r="F29" s="6">
+        <v>46235</v>
+      </c>
+      <c r="G29">
+        <v>15</v>
+      </c>
+      <c r="H29">
+        <v>34</v>
+      </c>
+      <c r="I29">
+        <v>8</v>
+      </c>
+      <c r="J29" t="s">
         <v>241</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C29" t="s">
-        <v>216</v>
-      </c>
-      <c r="D29" t="s">
-        <v>236</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" t="s">
-        <v>200</v>
-      </c>
-      <c r="C30" t="s">
-        <v>216</v>
-      </c>
-      <c r="D30" t="s">
-        <v>236</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
-        <v>115</v>
-      </c>
-      <c r="B31" t="s">
-        <v>201</v>
-      </c>
-      <c r="C31" t="s">
-        <v>216</v>
-      </c>
-      <c r="D31" t="s">
-        <v>236</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
-        <v>116</v>
-      </c>
-      <c r="B32" t="s">
-        <v>202</v>
-      </c>
-      <c r="C32" t="s">
-        <v>216</v>
-      </c>
-      <c r="D32" t="s">
-        <v>236</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" t="s">
-        <v>124</v>
-      </c>
-      <c r="C33" t="s">
-        <v>223</v>
-      </c>
-      <c r="D33" t="s">
-        <v>236</v>
-      </c>
-      <c r="E33">
-        <v>1.6</v>
-      </c>
-      <c r="F33">
-        <v>86</v>
-      </c>
-      <c r="G33" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" t="s">
-        <v>158</v>
-      </c>
-      <c r="C34" t="s">
-        <v>216</v>
-      </c>
-      <c r="D34" t="s">
-        <v>236</v>
-      </c>
-      <c r="E34">
-        <v>2.9</v>
-      </c>
-      <c r="F34">
-        <v>47</v>
-      </c>
-      <c r="G34" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" t="s">
-        <v>223</v>
-      </c>
-      <c r="D35" t="s">
-        <v>236</v>
-      </c>
-      <c r="E35">
-        <v>9.5</v>
-      </c>
-      <c r="F35">
-        <v>32</v>
-      </c>
-      <c r="G35" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" t="s">
-        <v>170</v>
-      </c>
-      <c r="C36" t="s">
-        <v>220</v>
-      </c>
-      <c r="D36" t="s">
-        <v>236</v>
-      </c>
-      <c r="E36">
-        <v>9.5</v>
-      </c>
-      <c r="F36">
-        <v>13</v>
-      </c>
-      <c r="G36" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" t="s">
-        <v>70</v>
-      </c>
-      <c r="B37" t="s">
-        <v>156</v>
-      </c>
-      <c r="C37" t="s">
-        <v>216</v>
-      </c>
-      <c r="D37" t="s">
-        <v>235</v>
-      </c>
-      <c r="E37">
-        <v>11.8</v>
-      </c>
-      <c r="F37">
-        <v>12</v>
-      </c>
-      <c r="G37" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" t="s">
-        <v>86</v>
-      </c>
-      <c r="B38" t="s">
-        <v>172</v>
-      </c>
-      <c r="C38" t="s">
-        <v>220</v>
-      </c>
-      <c r="D38" t="s">
-        <v>235</v>
-      </c>
-      <c r="E38">
-        <v>14.3</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" t="s">
-        <v>87</v>
-      </c>
-      <c r="B39" t="s">
-        <v>173</v>
-      </c>
-      <c r="C39" t="s">
-        <v>220</v>
-      </c>
-      <c r="D39" t="s">
-        <v>235</v>
-      </c>
-      <c r="E39">
-        <v>14.3</v>
-      </c>
-      <c r="F39">
-        <v>3</v>
-      </c>
-      <c r="G39" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" t="s">
-        <v>88</v>
-      </c>
-      <c r="B40" t="s">
-        <v>174</v>
-      </c>
-      <c r="C40" t="s">
-        <v>220</v>
-      </c>
-      <c r="D40" t="s">
-        <v>235</v>
-      </c>
-      <c r="E40">
-        <v>14.3</v>
-      </c>
-      <c r="F40">
-        <v>2</v>
-      </c>
-      <c r="G40" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" t="s">
-        <v>142</v>
-      </c>
-      <c r="C41" t="s">
-        <v>216</v>
-      </c>
-      <c r="D41" t="s">
-        <v>235</v>
-      </c>
-      <c r="E41">
-        <v>16.7</v>
-      </c>
-      <c r="F41">
-        <v>3</v>
-      </c>
-      <c r="G41" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" t="s">
-        <v>75</v>
-      </c>
-      <c r="B42" t="s">
-        <v>161</v>
-      </c>
-      <c r="C42" t="s">
-        <v>216</v>
-      </c>
-      <c r="D42" t="s">
-        <v>235</v>
-      </c>
-      <c r="E42">
-        <v>23.5</v>
-      </c>
-      <c r="F42">
-        <v>24</v>
-      </c>
-      <c r="G42" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" t="s">
-        <v>89</v>
-      </c>
-      <c r="B43" t="s">
-        <v>175</v>
-      </c>
-      <c r="C43" t="s">
-        <v>220</v>
-      </c>
-      <c r="D43" t="s">
-        <v>235</v>
-      </c>
-      <c r="E43">
-        <v>23.8</v>
-      </c>
-      <c r="F43">
-        <v>5</v>
-      </c>
-      <c r="G43" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" t="s">
-        <v>122</v>
-      </c>
-      <c r="C44" t="s">
-        <v>223</v>
-      </c>
-      <c r="D44" t="s">
-        <v>235</v>
-      </c>
-      <c r="E44">
-        <v>28.6</v>
-      </c>
-      <c r="F44">
-        <v>10</v>
-      </c>
-      <c r="G44" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45" t="s">
-        <v>117</v>
-      </c>
-      <c r="C45" t="s">
-        <v>223</v>
-      </c>
-      <c r="D45" t="s">
-        <v>235</v>
-      </c>
-      <c r="E45">
-        <v>30.2</v>
-      </c>
-      <c r="F45">
-        <v>4</v>
-      </c>
-      <c r="G45" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" t="s">
-        <v>69</v>
-      </c>
-      <c r="B46" t="s">
-        <v>155</v>
-      </c>
-      <c r="C46" t="s">
-        <v>216</v>
-      </c>
-      <c r="D46" t="s">
-        <v>235</v>
-      </c>
-      <c r="E46">
-        <v>32.4</v>
-      </c>
-      <c r="F46">
-        <v>6</v>
-      </c>
-      <c r="G46" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" t="s">
-        <v>120</v>
-      </c>
-      <c r="C47" t="s">
-        <v>223</v>
-      </c>
-      <c r="D47" t="s">
-        <v>235</v>
-      </c>
-      <c r="E47">
-        <v>33.3</v>
-      </c>
-      <c r="F47">
-        <v>2</v>
-      </c>
-      <c r="G47" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" t="s">
-        <v>83</v>
-      </c>
-      <c r="B48" t="s">
-        <v>169</v>
-      </c>
-      <c r="C48" t="s">
-        <v>220</v>
-      </c>
-      <c r="D48" t="s">
-        <v>235</v>
-      </c>
-      <c r="E48">
-        <v>33.3</v>
-      </c>
-      <c r="F48">
-        <v>19</v>
-      </c>
-      <c r="G48" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" t="s">
-        <v>121</v>
-      </c>
-      <c r="C49" t="s">
-        <v>223</v>
-      </c>
-      <c r="D49" t="s">
-        <v>235</v>
-      </c>
-      <c r="E49">
-        <v>34.9</v>
-      </c>
-      <c r="F49">
-        <v>2</v>
-      </c>
-      <c r="G49" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" t="s">
-        <v>127</v>
-      </c>
-      <c r="C50" t="s">
-        <v>223</v>
-      </c>
-      <c r="D50" t="s">
-        <v>235</v>
-      </c>
-      <c r="E50">
-        <v>36.5</v>
-      </c>
-      <c r="F50">
-        <v>3</v>
-      </c>
-      <c r="G50" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" t="s">
-        <v>60</v>
-      </c>
-      <c r="B51" t="s">
-        <v>143</v>
-      </c>
-      <c r="C51" t="s">
-        <v>216</v>
-      </c>
-      <c r="D51" t="s">
-        <v>235</v>
-      </c>
-      <c r="E51">
-        <v>41.7</v>
-      </c>
-      <c r="F51">
-        <v>3</v>
-      </c>
-      <c r="G51" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52" t="s">
-        <v>137</v>
-      </c>
-      <c r="C52" t="s">
-        <v>216</v>
-      </c>
-      <c r="D52" t="s">
-        <v>235</v>
-      </c>
-      <c r="E52">
-        <v>43.8</v>
-      </c>
-      <c r="F52">
-        <v>3</v>
-      </c>
-      <c r="G52" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" t="s">
-        <v>139</v>
-      </c>
-      <c r="C53" t="s">
-        <v>216</v>
-      </c>
-      <c r="D53" t="s">
-        <v>235</v>
-      </c>
-      <c r="E53">
-        <v>43.8</v>
-      </c>
-      <c r="F53">
-        <v>6</v>
-      </c>
-      <c r="G53" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" t="s">
-        <v>71</v>
-      </c>
-      <c r="B54" t="s">
-        <v>157</v>
-      </c>
-      <c r="C54" t="s">
-        <v>216</v>
-      </c>
-      <c r="D54" t="s">
-        <v>235</v>
-      </c>
-      <c r="E54">
-        <v>44.1</v>
-      </c>
-      <c r="F54">
-        <v>8</v>
-      </c>
-      <c r="G54" t="s">
-        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -12753,7 +12640,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -12761,10 +12648,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>8</v>
@@ -12998,7 +12885,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="8" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B15" s="8">
         <v>86</v>
@@ -13024,7 +12911,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="18.7109375" customWidth="1"/>
@@ -13033,7 +12920,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -13041,10 +12928,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -13096,10 +12983,209 @@
         <v>236</v>
       </c>
       <c r="B8">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>0.7</v>
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B9">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>107.9</v>
+      </c>
+      <c r="D4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>96.5</v>
+      </c>
+      <c r="D5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>81.8</v>
+      </c>
+      <c r="D6">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>69.8</v>
+      </c>
+      <c r="D7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>47.6</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B9">
+        <v>52</v>
+      </c>
+      <c r="C9">
+        <v>37.3</v>
+      </c>
+      <c r="D9">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>223</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>36.2</v>
+      </c>
+      <c r="D10">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>27.6</v>
+      </c>
+      <c r="D11">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>225</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Analisis_Usabilidad_Final.xlsx
+++ b/Analisis_Usabilidad_Final.xlsx
@@ -4113,7 +4113,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="4">
-        <v>960</v>
+        <v>1200</v>
       </c>
       <c r="E9" s="4">
         <v>1125.93</v>
@@ -4233,7 +4233,7 @@
         <v>85</v>
       </c>
       <c r="D15" s="6">
-        <v>26880</v>
+        <v>27120</v>
       </c>
       <c r="E15" s="6">
         <v>24351.75</v>
@@ -5637,7 +5637,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>960</v>
+        <v>1200</v>
       </c>
       <c r="J16">
         <v>1125.93</v>

--- a/Analisis_Usabilidad_Final.xlsx
+++ b/Analisis_Usabilidad_Final.xlsx
@@ -690,7 +690,7 @@
     <t>Costo por nivel de uso — monto ocioso vs productivo</t>
   </si>
   <si>
-    <t>Productivo (Muy Alto/Alto/Medio): 232,617.07 MXN   |   Ocioso (Bajo/Nulo): 131,577.40 MXN   |   En adopción (Reciente): 75,688.78 MXN</t>
+    <t>Productivo (Muy Alto/Alto/Medio): 232,617.07 MXN   |   Ocioso (Bajo/Nulo): 154,377.40 MXN   |   En adopción (Reciente): 75,688.78 MXN</t>
   </si>
   <si>
     <t>Resumen de aprovechamiento</t>
@@ -1800,7 +1800,7 @@
                   <c:v>88455.735</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>43121.6685</c:v>
+                  <c:v>65921.6685</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>75688.78</c:v>
@@ -1943,7 +1943,7 @@
                   <c:v>75688.78</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>131577.4035</c:v>
+                  <c:v>154377.4035</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6365,7 +6365,7 @@
         <v>69082.98666666666</v>
       </c>
       <c r="F6">
-        <v>15.7</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -6385,7 +6385,7 @@
         <v>96989.97291666667</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -6405,7 +6405,7 @@
         <v>66544.10691666667</v>
       </c>
       <c r="F8">
-        <v>15.1</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6425,7 +6425,7 @@
         <v>88455.735</v>
       </c>
       <c r="F9">
-        <v>20.1</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6436,16 +6436,16 @@
         <v>218</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="4">
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="E10" s="4">
-        <v>43121.6685</v>
+        <v>65921.6685</v>
       </c>
       <c r="F10">
-        <v>9.800000000000001</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -6465,7 +6465,7 @@
         <v>75688.78</v>
       </c>
       <c r="F11">
-        <v>17.2</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6474,13 +6474,13 @@
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D12" s="6">
-        <v>25920</v>
+        <v>27120</v>
       </c>
       <c r="E12" s="6">
-        <v>439883.25</v>
+        <v>462683.25</v>
       </c>
       <c r="F12" s="6">
         <v>100</v>
@@ -6522,7 +6522,7 @@
         <v>13200</v>
       </c>
       <c r="E15" s="4">
-        <v>52.9</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6539,7 +6539,7 @@
         <v>5280</v>
       </c>
       <c r="E16" s="4">
-        <v>17.2</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -6547,16 +6547,16 @@
         <v>218</v>
       </c>
       <c r="B17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17">
-        <v>131577.4035</v>
+        <v>154377.4035</v>
       </c>
       <c r="D17" s="4">
-        <v>7440</v>
+        <v>8640</v>
       </c>
       <c r="E17" s="4">
-        <v>29.9</v>
+        <v>33.4</v>
       </c>
     </row>
   </sheetData>

--- a/Analisis_Usabilidad_Final.xlsx
+++ b/Analisis_Usabilidad_Final.xlsx
@@ -186,150 +186,150 @@
     <t xml:space="preserve">Emma Alguera  </t>
   </si>
   <si>
+    <t>Alfonso Cueto</t>
+  </si>
+  <si>
+    <t>Omar Guzman</t>
+  </si>
+  <si>
+    <t>Bernardo González</t>
+  </si>
+  <si>
+    <t>Procurement Team</t>
+  </si>
+  <si>
+    <t>Sebastián González García</t>
+  </si>
+  <si>
+    <t>Hector Huerta</t>
+  </si>
+  <si>
+    <t>Ramiro Vazquez Vera</t>
+  </si>
+  <si>
+    <t>Jose Ivan Ramirez</t>
+  </si>
+  <si>
+    <t>Lizbeth Aguilar Morales</t>
+  </si>
+  <si>
+    <t>Aniver Chino Marcelino</t>
+  </si>
+  <si>
+    <t>Javier Loeza</t>
+  </si>
+  <si>
+    <t>Daniela Mondragon Corona</t>
+  </si>
+  <si>
+    <t>Victor Iván Soto Guerra</t>
+  </si>
+  <si>
+    <t>Miguel Angel Garrido Castaneda</t>
+  </si>
+  <si>
+    <t>Joaquin Calvo Leon</t>
+  </si>
+  <si>
+    <t>Jonathan Ramón</t>
+  </si>
+  <si>
+    <t>Jesus Morales Enciso</t>
+  </si>
+  <si>
+    <t>Edgar Fidel Salinas Espinoza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talia Maciel  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ricardo Laiseca  </t>
+  </si>
+  <si>
+    <t>Marco Espinosa</t>
+  </si>
+  <si>
+    <t>Ricardo Santiago</t>
+  </si>
+  <si>
+    <t>Mercedes Morales</t>
+  </si>
+  <si>
+    <t>Hector Espejel</t>
+  </si>
+  <si>
+    <t>Bruno Juanes</t>
+  </si>
+  <si>
+    <t>Maghandi Suarez</t>
+  </si>
+  <si>
+    <t>Marketing Team</t>
+  </si>
+  <si>
+    <t>Gustavo Gonzalez Martinez</t>
+  </si>
+  <si>
+    <t>Sandy Areli Monroy</t>
+  </si>
+  <si>
+    <t>Juan Carlos Morales Leon</t>
+  </si>
+  <si>
+    <t>Erwin Ordonez Velazquez</t>
+  </si>
+  <si>
+    <t>Nathalie Reyes</t>
+  </si>
+  <si>
+    <t>Raul Jaimes Martin</t>
+  </si>
+  <si>
+    <t>Luis Montes</t>
+  </si>
+  <si>
+    <t>José Ríos Alonso</t>
+  </si>
+  <si>
+    <t>Christian Jesus Ocampo Arce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodrigo Galindo Mello </t>
+  </si>
+  <si>
+    <t>Aldo Romero</t>
+  </si>
+  <si>
+    <t>Gerardo Tellez</t>
+  </si>
+  <si>
+    <t>Rafael Sánchez</t>
+  </si>
+  <si>
+    <t>Rafael Hernández</t>
+  </si>
+  <si>
+    <t>Abraham Espinal</t>
+  </si>
+  <si>
+    <t>Jonathan Vallejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olga Badillo </t>
+  </si>
+  <si>
+    <t>Edwin Medina</t>
+  </si>
+  <si>
+    <t>Javier Reyes</t>
+  </si>
+  <si>
+    <t>Armando Beltran</t>
+  </si>
+  <si>
     <t>José Da Silva</t>
   </si>
   <si>
-    <t>Alfonso Cueto</t>
-  </si>
-  <si>
-    <t>Omar Guzman</t>
-  </si>
-  <si>
-    <t>Bernardo González</t>
-  </si>
-  <si>
-    <t>Procurement Team</t>
-  </si>
-  <si>
-    <t>Sebastián González García</t>
-  </si>
-  <si>
-    <t>Hector Huerta</t>
-  </si>
-  <si>
-    <t>Ramiro Vazquez Vera</t>
-  </si>
-  <si>
-    <t>Jose Ivan Ramirez</t>
-  </si>
-  <si>
-    <t>Lizbeth Aguilar Morales</t>
-  </si>
-  <si>
-    <t>Aniver Chino Marcelino</t>
-  </si>
-  <si>
-    <t>Javier Loeza</t>
-  </si>
-  <si>
-    <t>Daniela Mondragon Corona</t>
-  </si>
-  <si>
-    <t>Victor Iván Soto Guerra</t>
-  </si>
-  <si>
-    <t>Miguel Angel Garrido Castaneda</t>
-  </si>
-  <si>
-    <t>Joaquin Calvo Leon</t>
-  </si>
-  <si>
-    <t>Jonathan Ramón</t>
-  </si>
-  <si>
-    <t>Jesus Morales Enciso</t>
-  </si>
-  <si>
-    <t>Edgar Fidel Salinas Espinoza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talia Maciel  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ricardo Laiseca  </t>
-  </si>
-  <si>
-    <t>Marco Espinosa</t>
-  </si>
-  <si>
-    <t>Ricardo Santiago</t>
-  </si>
-  <si>
-    <t>Mercedes Morales</t>
-  </si>
-  <si>
-    <t>Hector Espejel</t>
-  </si>
-  <si>
-    <t>Bruno Juanes</t>
-  </si>
-  <si>
-    <t>Maghandi Suarez</t>
-  </si>
-  <si>
-    <t>Marketing Team</t>
-  </si>
-  <si>
-    <t>Gustavo Gonzalez Martinez</t>
-  </si>
-  <si>
-    <t>Sandy Areli Monroy</t>
-  </si>
-  <si>
-    <t>Juan Carlos Morales Leon</t>
-  </si>
-  <si>
-    <t>Erwin Ordonez Velazquez</t>
-  </si>
-  <si>
-    <t>Nathalie Reyes</t>
-  </si>
-  <si>
-    <t>Raul Jaimes Martin</t>
-  </si>
-  <si>
-    <t>Luis Montes</t>
-  </si>
-  <si>
-    <t>José Ríos Alonso</t>
-  </si>
-  <si>
-    <t>Christian Jesus Ocampo Arce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rodrigo Galindo Mello </t>
-  </si>
-  <si>
-    <t>Aldo Romero</t>
-  </si>
-  <si>
-    <t>Gerardo Tellez</t>
-  </si>
-  <si>
-    <t>Rafael Sánchez</t>
-  </si>
-  <si>
-    <t>Rafael Hernández</t>
-  </si>
-  <si>
-    <t>Abraham Espinal</t>
-  </si>
-  <si>
-    <t>Jonathan Vallejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olga Badillo </t>
-  </si>
-  <si>
-    <t>Edwin Medina</t>
-  </si>
-  <si>
-    <t>Javier Reyes</t>
-  </si>
-  <si>
-    <t>Armando Beltran</t>
-  </si>
-  <si>
     <t>Ossiel Cruz Velazquez</t>
   </si>
   <si>
@@ -441,150 +441,150 @@
     <t>ealguera@kio.tech</t>
   </si>
   <si>
+    <t>acueto@kio.tech</t>
+  </si>
+  <si>
+    <t>oguzmant@kio.tech</t>
+  </si>
+  <si>
+    <t>jbgonzalez@kio.tech</t>
+  </si>
+  <si>
+    <t>compras_proyectos@kio.tech</t>
+  </si>
+  <si>
+    <t>sgonzalezg@kio.tech</t>
+  </si>
+  <si>
+    <t>hhuerta@kio.tech</t>
+  </si>
+  <si>
+    <t>rvazquez@kio.tech</t>
+  </si>
+  <si>
+    <t>jramirezl@kio.tech</t>
+  </si>
+  <si>
+    <t>laguilar@kio.tech</t>
+  </si>
+  <si>
+    <t>achino@kio.tech</t>
+  </si>
+  <si>
+    <t>jloeza@kio.tech</t>
+  </si>
+  <si>
+    <t>dmondragon@kio.tech</t>
+  </si>
+  <si>
+    <t>vsoto@kio.tech</t>
+  </si>
+  <si>
+    <t>mgarrido@kio.tech</t>
+  </si>
+  <si>
+    <t>jcalvo@kio.tech</t>
+  </si>
+  <si>
+    <t>jramon@kio.tech</t>
+  </si>
+  <si>
+    <t>jmoralese@kio.tech</t>
+  </si>
+  <si>
+    <t>esalinas@kio.tech</t>
+  </si>
+  <si>
+    <t>tmaciel@kio.tech</t>
+  </si>
+  <si>
+    <t>rilaiseca@kio.tech</t>
+  </si>
+  <si>
+    <t>mespinosa@kio.tech</t>
+  </si>
+  <si>
+    <t>rsantiago@kio.tech</t>
+  </si>
+  <si>
+    <t>mmoralesl@kio.tech</t>
+  </si>
+  <si>
+    <t>hespejel@kio.tech</t>
+  </si>
+  <si>
+    <t>bjuanes@kio.tech</t>
+  </si>
+  <si>
+    <t>msuarezp@kio.tech</t>
+  </si>
+  <si>
+    <t>marketing@kio.tech</t>
+  </si>
+  <si>
+    <t>ggonzalez@kio.tech</t>
+  </si>
+  <si>
+    <t>smonroy@kio.tech</t>
+  </si>
+  <si>
+    <t>jcmorales@kio.tech</t>
+  </si>
+  <si>
+    <t>eordonez@kio.tech</t>
+  </si>
+  <si>
+    <t>nreyesz@kio.tech</t>
+  </si>
+  <si>
+    <t>rjaimes@kio.tech</t>
+  </si>
+  <si>
+    <t>lmontes@kio.tech</t>
+  </si>
+  <si>
+    <t>jriosa@kio.tech</t>
+  </si>
+  <si>
+    <t>cocampo@kio.tech</t>
+  </si>
+  <si>
+    <t>rgalindo@kio.tech</t>
+  </si>
+  <si>
+    <t>aromero@kio.tech</t>
+  </si>
+  <si>
+    <t>gtellez@kio.tech</t>
+  </si>
+  <si>
+    <t>rsanchezo@kio.tech</t>
+  </si>
+  <si>
+    <t>rhernandezb@kio.tech</t>
+  </si>
+  <si>
+    <t>aespinal@kio.tech</t>
+  </si>
+  <si>
+    <t>jjvallejo@kio.tech</t>
+  </si>
+  <si>
+    <t>obadillo@kio.tech</t>
+  </si>
+  <si>
+    <t>emedina@kio.tech</t>
+  </si>
+  <si>
+    <t>jreyes@kio.tech</t>
+  </si>
+  <si>
+    <t>abeltran@kio.tech</t>
+  </si>
+  <si>
     <t>jdasilva@kio.tech</t>
   </si>
   <si>
-    <t>acueto@kio.tech</t>
-  </si>
-  <si>
-    <t>oguzmant@kio.tech</t>
-  </si>
-  <si>
-    <t>jbgonzalez@kio.tech</t>
-  </si>
-  <si>
-    <t>compras_proyectos@kio.tech</t>
-  </si>
-  <si>
-    <t>sgonzalezg@kio.tech</t>
-  </si>
-  <si>
-    <t>hhuerta@kio.tech</t>
-  </si>
-  <si>
-    <t>rvazquez@kio.tech</t>
-  </si>
-  <si>
-    <t>jramirezl@kio.tech</t>
-  </si>
-  <si>
-    <t>laguilar@kio.tech</t>
-  </si>
-  <si>
-    <t>achino@kio.tech</t>
-  </si>
-  <si>
-    <t>jloeza@kio.tech</t>
-  </si>
-  <si>
-    <t>dmondragon@kio.tech</t>
-  </si>
-  <si>
-    <t>vsoto@kio.tech</t>
-  </si>
-  <si>
-    <t>mgarrido@kio.tech</t>
-  </si>
-  <si>
-    <t>jcalvo@kio.tech</t>
-  </si>
-  <si>
-    <t>jramon@kio.tech</t>
-  </si>
-  <si>
-    <t>jmoralese@kio.tech</t>
-  </si>
-  <si>
-    <t>esalinas@kio.tech</t>
-  </si>
-  <si>
-    <t>tmaciel@kio.tech</t>
-  </si>
-  <si>
-    <t>rilaiseca@kio.tech</t>
-  </si>
-  <si>
-    <t>mespinosa@kio.tech</t>
-  </si>
-  <si>
-    <t>rsantiago@kio.tech</t>
-  </si>
-  <si>
-    <t>mmoralesl@kio.tech</t>
-  </si>
-  <si>
-    <t>hespejel@kio.tech</t>
-  </si>
-  <si>
-    <t>bjuanes@kio.tech</t>
-  </si>
-  <si>
-    <t>msuarezp@kio.tech</t>
-  </si>
-  <si>
-    <t>marketing@kio.tech</t>
-  </si>
-  <si>
-    <t>ggonzalez@kio.tech</t>
-  </si>
-  <si>
-    <t>smonroy@kio.tech</t>
-  </si>
-  <si>
-    <t>jcmorales@kio.tech</t>
-  </si>
-  <si>
-    <t>eordonez@kio.tech</t>
-  </si>
-  <si>
-    <t>nreyesz@kio.tech</t>
-  </si>
-  <si>
-    <t>rjaimes@kio.tech</t>
-  </si>
-  <si>
-    <t>lmontes@kio.tech</t>
-  </si>
-  <si>
-    <t>jriosa@kio.tech</t>
-  </si>
-  <si>
-    <t>cocampo@kio.tech</t>
-  </si>
-  <si>
-    <t>rgalindo@kio.tech</t>
-  </si>
-  <si>
-    <t>aromero@kio.tech</t>
-  </si>
-  <si>
-    <t>gtellez@kio.tech</t>
-  </si>
-  <si>
-    <t>rsanchezo@kio.tech</t>
-  </si>
-  <si>
-    <t>rhernandezb@kio.tech</t>
-  </si>
-  <si>
-    <t>aespinal@kio.tech</t>
-  </si>
-  <si>
-    <t>jjvallejo@kio.tech</t>
-  </si>
-  <si>
-    <t>obadillo@kio.tech</t>
-  </si>
-  <si>
-    <t>emedina@kio.tech</t>
-  </si>
-  <si>
-    <t>jreyes@kio.tech</t>
-  </si>
-  <si>
-    <t>abeltran@kio.tech</t>
-  </si>
-  <si>
     <t>ocruzv@kio.tech</t>
   </si>
   <si>
@@ -699,7 +699,7 @@
     <t>Costo por nivel de uso — monto ocioso vs productivo</t>
   </si>
   <si>
-    <t>Productivo (Muy Alto/Alto/Medio): 276,279.81 MXN   |   Ocioso (Bajo/Nulo): 141,129.76 MXN   |   En adopción (Reciente): 45,273.68 MXN</t>
+    <t>Productivo (Muy Alto/Alto/Medio): 272,848.95 MXN   |   Ocioso (Bajo/Nulo): 141,129.76 MXN   |   En adopción (Reciente): 48,704.54 MXN</t>
   </si>
   <si>
     <t>Resumen de aprovechamiento</t>
@@ -1494,7 +1494,7 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>22</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>22</c:v>
@@ -1503,7 +1503,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>13</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1621,10 +1621,10 @@
                   <c:v>Marketing</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Dir Ops</c:v>
+                  <c:v>Dirección</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Dirección</c:v>
+                  <c:v>Dir Ops</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>Ops - Plataformas</c:v>
@@ -1666,10 +1666,10 @@
                   <c:v>41.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>40.8</c:v>
+                  <c:v>37.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>37.6</c:v>
+                  <c:v>33.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>29.6</c:v>
@@ -1851,7 +1851,7 @@
                   <c:v>93794.42941666667</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>104004.2029166667</c:v>
+                  <c:v>100573.3444166667</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>106863.8185</c:v>
@@ -1860,7 +1860,7 @@
                   <c:v>34265.94425</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>45273.67975</c:v>
+                  <c:v>48704.53825</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1994,10 +1994,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>276279.8075</c:v>
+                  <c:v>272848.949</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45273.67975</c:v>
+                  <c:v>48704.53825</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>141129.76275</c:v>
@@ -4080,19 +4080,22 @@
         <v>201</v>
       </c>
       <c r="E28">
-        <v>50</v>
+        <v>53.8</v>
+      </c>
+      <c r="F28" s="3">
+        <v>46230</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="I28">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="J28">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K28" t="s">
         <v>205</v>
@@ -4112,22 +4115,22 @@
         <v>201</v>
       </c>
       <c r="E29">
-        <v>53.8</v>
+        <v>66.2</v>
       </c>
       <c r="F29" s="3">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="G29">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="I29">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="J29">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K29" t="s">
         <v>205</v>
@@ -4135,7 +4138,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
         <v>55</v>
@@ -4147,22 +4150,22 @@
         <v>201</v>
       </c>
       <c r="E30">
-        <v>66.2</v>
+        <v>54.4</v>
       </c>
       <c r="F30" s="3">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="I30">
         <v>68</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="s">
         <v>205</v>
@@ -4170,7 +4173,7 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
         <v>56</v>
@@ -4182,22 +4185,22 @@
         <v>201</v>
       </c>
       <c r="E31">
-        <v>54.4</v>
+        <v>48.9</v>
       </c>
       <c r="F31" s="3">
-        <v>46250</v>
+        <v>46247</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I31">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="s">
         <v>205</v>
@@ -4205,7 +4208,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
         <v>57</v>
@@ -4217,22 +4220,22 @@
         <v>201</v>
       </c>
       <c r="E32">
-        <v>48.9</v>
+        <v>69.7</v>
       </c>
       <c r="F32" s="3">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32">
         <v>23</v>
       </c>
       <c r="I32">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" t="s">
         <v>205</v>
@@ -4240,7 +4243,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
         <v>58</v>
@@ -4252,7 +4255,7 @@
         <v>201</v>
       </c>
       <c r="E33">
-        <v>69.7</v>
+        <v>47.2</v>
       </c>
       <c r="F33" s="3">
         <v>46248</v>
@@ -4261,10 +4264,10 @@
         <v>2</v>
       </c>
       <c r="H33">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I33">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -4287,7 +4290,7 @@
         <v>201</v>
       </c>
       <c r="E34">
-        <v>47.2</v>
+        <v>49.1</v>
       </c>
       <c r="F34" s="3">
         <v>46248</v>
@@ -4296,7 +4299,7 @@
         <v>2</v>
       </c>
       <c r="H34">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I34">
         <v>53</v>
@@ -4325,10 +4328,10 @@
         <v>49.1</v>
       </c>
       <c r="F35" s="3">
-        <v>46248</v>
+        <v>46245</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H35">
         <v>26</v>
@@ -4337,7 +4340,7 @@
         <v>53</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K35" t="s">
         <v>205</v>
@@ -4357,22 +4360,22 @@
         <v>201</v>
       </c>
       <c r="E36">
-        <v>49.1</v>
+        <v>50</v>
       </c>
       <c r="F36" s="3">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="I36">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K36" t="s">
         <v>205</v>
@@ -4395,10 +4398,10 @@
         <v>50</v>
       </c>
       <c r="F37" s="3">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37">
         <v>2</v>
@@ -4407,7 +4410,7 @@
         <v>4</v>
       </c>
       <c r="J37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K37" t="s">
         <v>205</v>
@@ -4430,10 +4433,10 @@
         <v>50</v>
       </c>
       <c r="F38" s="3">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38">
         <v>2</v>
@@ -4442,7 +4445,7 @@
         <v>4</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" t="s">
         <v>205</v>
@@ -4462,7 +4465,7 @@
         <v>201</v>
       </c>
       <c r="E39">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="F39" s="3">
         <v>46247</v>
@@ -4471,10 +4474,10 @@
         <v>3</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="J39">
         <v>2</v>
@@ -4497,22 +4500,22 @@
         <v>201</v>
       </c>
       <c r="E40">
-        <v>50.9</v>
+        <v>52.9</v>
       </c>
       <c r="F40" s="3">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H40">
         <v>27</v>
       </c>
       <c r="I40">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K40" t="s">
         <v>205</v>
@@ -4532,22 +4535,22 @@
         <v>201</v>
       </c>
       <c r="E41">
-        <v>52.9</v>
+        <v>60.4</v>
       </c>
       <c r="F41" s="3">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H41">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="I41">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K41" t="s">
         <v>205</v>
@@ -4567,22 +4570,22 @@
         <v>201</v>
       </c>
       <c r="E42">
-        <v>60.4</v>
+        <v>61.5</v>
       </c>
       <c r="F42" s="3">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="G42">
+        <v>4</v>
+      </c>
+      <c r="H42">
+        <v>24</v>
+      </c>
+      <c r="I42">
+        <v>39</v>
+      </c>
+      <c r="J42">
         <v>3</v>
-      </c>
-      <c r="H42">
-        <v>32</v>
-      </c>
-      <c r="I42">
-        <v>53</v>
-      </c>
-      <c r="J42">
-        <v>2</v>
       </c>
       <c r="K42" t="s">
         <v>205</v>
@@ -4602,22 +4605,22 @@
         <v>201</v>
       </c>
       <c r="E43">
-        <v>61.5</v>
+        <v>62.3</v>
       </c>
       <c r="F43" s="3">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H43">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I43">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K43" t="s">
         <v>205</v>
@@ -4625,7 +4628,7 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B44" t="s">
         <v>69</v>
@@ -4637,22 +4640,22 @@
         <v>201</v>
       </c>
       <c r="E44">
-        <v>62.3</v>
+        <v>50</v>
       </c>
       <c r="F44" s="3">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="G44">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H44">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="I44">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="J44">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K44" t="s">
         <v>205</v>
@@ -4672,22 +4675,22 @@
         <v>201</v>
       </c>
       <c r="E45">
-        <v>50</v>
+        <v>57.7</v>
       </c>
       <c r="F45" s="3">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I45">
         <v>26</v>
       </c>
       <c r="J45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" t="s">
         <v>205</v>
@@ -4695,7 +4698,7 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
         <v>71</v>
@@ -4707,22 +4710,22 @@
         <v>201</v>
       </c>
       <c r="E46">
-        <v>57.7</v>
+        <v>50</v>
       </c>
       <c r="F46" s="3">
-        <v>46248</v>
+        <v>46247</v>
       </c>
       <c r="G46">
+        <v>3</v>
+      </c>
+      <c r="H46">
+        <v>3</v>
+      </c>
+      <c r="I46">
+        <v>6</v>
+      </c>
+      <c r="J46">
         <v>2</v>
-      </c>
-      <c r="H46">
-        <v>15</v>
-      </c>
-      <c r="I46">
-        <v>26</v>
-      </c>
-      <c r="J46">
-        <v>1</v>
       </c>
       <c r="K46" t="s">
         <v>205</v>
@@ -4777,7 +4780,7 @@
         <v>201</v>
       </c>
       <c r="E48">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="F48" s="3">
         <v>46247</v>
@@ -4786,7 +4789,7 @@
         <v>3</v>
       </c>
       <c r="H48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I48">
         <v>6</v>
@@ -4800,7 +4803,7 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
         <v>74</v>
@@ -4809,33 +4812,33 @@
         <v>159</v>
       </c>
       <c r="D49" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E49">
-        <v>66.7</v>
+        <v>20.5</v>
       </c>
       <c r="F49" s="3">
-        <v>46247</v>
+        <v>46219</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I49">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="J49">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K49" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
         <v>75</v>
@@ -4847,22 +4850,22 @@
         <v>202</v>
       </c>
       <c r="E50">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="F50" s="3">
-        <v>46219</v>
+        <v>46245</v>
       </c>
       <c r="G50">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H50">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I50">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="J50">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="K50" t="s">
         <v>206</v>
@@ -4882,22 +4885,22 @@
         <v>202</v>
       </c>
       <c r="E51">
-        <v>23.5</v>
+        <v>27.9</v>
       </c>
       <c r="F51" s="3">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H51">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I51">
         <v>68</v>
       </c>
       <c r="J51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K51" t="s">
         <v>206</v>
@@ -4917,7 +4920,7 @@
         <v>202</v>
       </c>
       <c r="E52">
-        <v>27.9</v>
+        <v>29.4</v>
       </c>
       <c r="F52" s="3">
         <v>46247</v>
@@ -4926,7 +4929,7 @@
         <v>3</v>
       </c>
       <c r="H52">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I52">
         <v>68</v>
@@ -4952,22 +4955,22 @@
         <v>202</v>
       </c>
       <c r="E53">
-        <v>29.4</v>
+        <v>33.8</v>
       </c>
       <c r="F53" s="3">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I53">
         <v>68</v>
       </c>
       <c r="J53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K53" t="s">
         <v>206</v>
@@ -4975,7 +4978,7 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
         <v>79</v>
@@ -4987,22 +4990,22 @@
         <v>202</v>
       </c>
       <c r="E54">
-        <v>33.8</v>
+        <v>41.2</v>
       </c>
       <c r="F54" s="3">
-        <v>46248</v>
+        <v>46250</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I54">
         <v>68</v>
       </c>
       <c r="J54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="s">
         <v>206</v>
@@ -5010,7 +5013,7 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B55" t="s">
         <v>80</v>
@@ -5022,22 +5025,22 @@
         <v>202</v>
       </c>
       <c r="E55">
-        <v>41.2</v>
+        <v>10.3</v>
       </c>
       <c r="F55" s="3">
-        <v>46250</v>
+        <v>46231</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H55">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I55">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K55" t="s">
         <v>206</v>
@@ -5057,22 +5060,22 @@
         <v>202</v>
       </c>
       <c r="E56">
-        <v>10.3</v>
+        <v>17</v>
       </c>
       <c r="F56" s="3">
-        <v>46231</v>
+        <v>46245</v>
       </c>
       <c r="G56">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H56">
+        <v>9</v>
+      </c>
+      <c r="I56">
+        <v>53</v>
+      </c>
+      <c r="J56">
         <v>4</v>
-      </c>
-      <c r="I56">
-        <v>39</v>
-      </c>
-      <c r="J56">
-        <v>14</v>
       </c>
       <c r="K56" t="s">
         <v>206</v>
@@ -5092,22 +5095,22 @@
         <v>202</v>
       </c>
       <c r="E57">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F57" s="3">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H57">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K57" t="s">
         <v>206</v>
@@ -5165,10 +5168,10 @@
         <v>25</v>
       </c>
       <c r="F59" s="3">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -5177,7 +5180,7 @@
         <v>4</v>
       </c>
       <c r="J59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K59" t="s">
         <v>206</v>
@@ -5197,22 +5200,22 @@
         <v>202</v>
       </c>
       <c r="E60">
-        <v>25</v>
+        <v>28.2</v>
       </c>
       <c r="F60" s="3">
-        <v>46248</v>
+        <v>46237</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I60">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K60" t="s">
         <v>206</v>
@@ -5232,22 +5235,22 @@
         <v>202</v>
       </c>
       <c r="E61">
-        <v>28.2</v>
+        <v>41.5</v>
       </c>
       <c r="F61" s="3">
-        <v>46237</v>
+        <v>46249</v>
       </c>
       <c r="G61">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I61">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J61">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K61" t="s">
         <v>206</v>
@@ -5267,22 +5270,22 @@
         <v>202</v>
       </c>
       <c r="E62">
-        <v>41.5</v>
+        <v>43.4</v>
       </c>
       <c r="F62" s="3">
-        <v>46249</v>
+        <v>46223</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="H62">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I62">
         <v>53</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K62" t="s">
         <v>206</v>
@@ -5302,22 +5305,22 @@
         <v>202</v>
       </c>
       <c r="E63">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="F63" s="3">
-        <v>46223</v>
+        <v>46248</v>
       </c>
       <c r="G63">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H63">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I63">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J63">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K63" t="s">
         <v>206</v>
@@ -5325,7 +5328,7 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B64" t="s">
         <v>89</v>
@@ -5337,22 +5340,22 @@
         <v>202</v>
       </c>
       <c r="E64">
-        <v>43.6</v>
+        <v>14.3</v>
       </c>
       <c r="F64" s="3">
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H64">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="J64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K64" t="s">
         <v>206</v>
@@ -5360,7 +5363,7 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B65" t="s">
         <v>90</v>
@@ -5372,22 +5375,22 @@
         <v>202</v>
       </c>
       <c r="E65">
-        <v>14.3</v>
+        <v>11.5</v>
       </c>
       <c r="F65" s="3">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="G65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K65" t="s">
         <v>206</v>
@@ -5410,10 +5413,10 @@
         <v>11.5</v>
       </c>
       <c r="F66" s="3">
-        <v>46246</v>
+        <v>46240</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H66">
         <v>3</v>
@@ -5422,7 +5425,7 @@
         <v>26</v>
       </c>
       <c r="J66">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K66" t="s">
         <v>206</v>
@@ -5445,10 +5448,10 @@
         <v>11.5</v>
       </c>
       <c r="F67" s="3">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="G67">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H67">
         <v>3</v>
@@ -5457,7 +5460,7 @@
         <v>26</v>
       </c>
       <c r="J67">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K67" t="s">
         <v>206</v>
@@ -5477,22 +5480,22 @@
         <v>202</v>
       </c>
       <c r="E68">
-        <v>11.5</v>
+        <v>19.2</v>
       </c>
       <c r="F68" s="3">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="G68">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I68">
         <v>26</v>
       </c>
       <c r="J68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K68" t="s">
         <v>206</v>
@@ -5515,10 +5518,10 @@
         <v>19.2</v>
       </c>
       <c r="F69" s="3">
-        <v>46245</v>
+        <v>46238</v>
       </c>
       <c r="G69">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H69">
         <v>5</v>
@@ -5527,7 +5530,7 @@
         <v>26</v>
       </c>
       <c r="J69">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K69" t="s">
         <v>206</v>
@@ -5547,22 +5550,22 @@
         <v>202</v>
       </c>
       <c r="E70">
-        <v>19.2</v>
+        <v>34.6</v>
       </c>
       <c r="F70" s="3">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="G70">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H70">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I70">
         <v>26</v>
       </c>
       <c r="J70">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K70" t="s">
         <v>206</v>
@@ -5570,7 +5573,7 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B71" t="s">
         <v>96</v>
@@ -5579,28 +5582,25 @@
         <v>181</v>
       </c>
       <c r="D71" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E71">
-        <v>34.6</v>
-      </c>
-      <c r="F71" s="3">
-        <v>46245</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H71">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I71">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J71">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K71" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -5617,19 +5617,22 @@
         <v>203</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>2.6</v>
+      </c>
+      <c r="F72" s="3">
+        <v>46249</v>
       </c>
       <c r="G72">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="J72">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K72" t="s">
         <v>207</v>
@@ -5637,7 +5640,7 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B73" t="s">
         <v>98</v>
@@ -5649,22 +5652,19 @@
         <v>203</v>
       </c>
       <c r="E73">
-        <v>2.6</v>
-      </c>
-      <c r="F73" s="3">
-        <v>46249</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="K73" t="s">
         <v>207</v>
@@ -5672,7 +5672,7 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B74" t="s">
         <v>99</v>
@@ -5684,19 +5684,22 @@
         <v>203</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>3.8</v>
+      </c>
+      <c r="F74" s="3">
+        <v>46247</v>
       </c>
       <c r="G74">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="J74">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="K74" t="s">
         <v>207</v>
@@ -5704,7 +5707,7 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B75" t="s">
         <v>100</v>
@@ -5713,28 +5716,25 @@
         <v>185</v>
       </c>
       <c r="D75" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E75">
-        <v>3.8</v>
-      </c>
-      <c r="F75" s="3">
-        <v>46247</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K75" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -6211,10 +6211,10 @@
         <v>201</v>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6">
-        <v>54.6</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6244,7 +6244,7 @@
         <v>204</v>
       </c>
       <c r="B9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -6384,30 +6384,30 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>7</v>
       </c>
       <c r="C11">
-        <v>40.8</v>
+        <v>37.6</v>
       </c>
       <c r="D11">
-        <v>16.1</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>7</v>
       </c>
       <c r="C12">
-        <v>37.6</v>
+        <v>33.6</v>
       </c>
       <c r="D12">
-        <v>25.6</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6546,16 +6546,16 @@
         <v>220</v>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4">
-        <v>5040</v>
+        <v>4800</v>
       </c>
       <c r="E8" s="4">
-        <v>104004.2029166667</v>
+        <v>100573.3444166667</v>
       </c>
       <c r="F8">
-        <v>22.5</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -6606,16 +6606,16 @@
         <v>222</v>
       </c>
       <c r="C11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" s="4">
-        <v>3120</v>
+        <v>3360</v>
       </c>
       <c r="E11" s="4">
-        <v>45273.67975</v>
+        <v>48704.53825</v>
       </c>
       <c r="F11">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -6663,16 +6663,16 @@
         <v>220</v>
       </c>
       <c r="B15">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15">
-        <v>276279.8075</v>
+        <v>272848.949</v>
       </c>
       <c r="D15" s="4">
-        <v>14640</v>
+        <v>14400</v>
       </c>
       <c r="E15" s="4">
-        <v>59.7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -6680,16 +6680,16 @@
         <v>222</v>
       </c>
       <c r="B16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16">
-        <v>45273.67975</v>
+        <v>48704.53825</v>
       </c>
       <c r="D16" s="4">
-        <v>3120</v>
+        <v>3360</v>
       </c>
       <c r="E16" s="4">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7398,10 +7398,10 @@
     </row>
     <row r="5" spans="1:40">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
         <v>262</v>
@@ -7517,10 +7517,10 @@
     </row>
     <row r="6" spans="1:40">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>262</v>
@@ -7636,10 +7636,10 @@
     </row>
     <row r="7" spans="1:40">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C7" t="s">
         <v>262</v>
@@ -7755,10 +7755,10 @@
     </row>
     <row r="8" spans="1:40">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C8" t="s">
         <v>262</v>
@@ -7874,10 +7874,10 @@
     </row>
     <row r="9" spans="1:40">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C9" t="s">
         <v>262</v>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="11" spans="1:40">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C11" t="s">
         <v>262</v>
@@ -8151,10 +8151,10 @@
         <v>46155</v>
       </c>
       <c r="N11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -8466,10 +8466,10 @@
     </row>
     <row r="14" spans="1:40">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C14" t="s">
         <v>262</v>
@@ -8585,10 +8585,10 @@
     </row>
     <row r="15" spans="1:40">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C15" t="s">
         <v>262</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="16" spans="1:40">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C16" t="s">
         <v>263</v>
@@ -9061,10 +9061,10 @@
     </row>
     <row r="19" spans="1:40">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" t="s">
         <v>263</v>
@@ -9418,10 +9418,10 @@
     </row>
     <row r="22" spans="1:40">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
         <v>263</v>
@@ -9537,10 +9537,10 @@
     </row>
     <row r="23" spans="1:40">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C23" t="s">
         <v>263</v>
@@ -9775,10 +9775,10 @@
     </row>
     <row r="25" spans="1:40">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
         <v>264</v>
@@ -10132,10 +10132,10 @@
     </row>
     <row r="28" spans="1:40">
       <c r="A28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
         <v>264</v>
@@ -10251,10 +10251,10 @@
     </row>
     <row r="29" spans="1:40">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C29" t="s">
         <v>264</v>
@@ -10370,10 +10370,10 @@
     </row>
     <row r="30" spans="1:40">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C30" t="s">
         <v>264</v>
@@ -10489,10 +10489,10 @@
     </row>
     <row r="31" spans="1:40">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C31" t="s">
         <v>264</v>
@@ -10608,10 +10608,10 @@
     </row>
     <row r="32" spans="1:40">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C32" t="s">
         <v>265</v>
@@ -10846,10 +10846,10 @@
     </row>
     <row r="34" spans="1:40">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C34" t="s">
         <v>267</v>
@@ -10965,10 +10965,10 @@
     </row>
     <row r="35" spans="1:40">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
         <v>268</v>
@@ -11560,10 +11560,10 @@
     </row>
     <row r="40" spans="1:40">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C40" t="s">
         <v>268</v>
@@ -11679,10 +11679,10 @@
     </row>
     <row r="41" spans="1:40">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C41" t="s">
         <v>268</v>
@@ -11798,10 +11798,10 @@
     </row>
     <row r="42" spans="1:40">
       <c r="A42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C42" t="s">
         <v>268</v>
@@ -12036,10 +12036,10 @@
     </row>
     <row r="44" spans="1:40">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
         <v>268</v>
@@ -12155,10 +12155,10 @@
     </row>
     <row r="45" spans="1:40">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C45" t="s">
         <v>268</v>
@@ -12274,10 +12274,10 @@
     </row>
     <row r="46" spans="1:40">
       <c r="A46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C46" t="s">
         <v>268</v>
@@ -12631,10 +12631,10 @@
     </row>
     <row r="49" spans="1:40">
       <c r="A49" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
         <v>269</v>
@@ -12869,10 +12869,10 @@
     </row>
     <row r="51" spans="1:40">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C51" t="s">
         <v>267</v>
@@ -12988,10 +12988,10 @@
     </row>
     <row r="52" spans="1:40">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C52" t="s">
         <v>267</v>
@@ -13107,10 +13107,10 @@
     </row>
     <row r="53" spans="1:40">
       <c r="A53" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B53" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C53" t="s">
         <v>267</v>
@@ -13226,10 +13226,10 @@
     </row>
     <row r="54" spans="1:40">
       <c r="A54" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C54" t="s">
         <v>267</v>
@@ -13345,10 +13345,10 @@
     </row>
     <row r="55" spans="1:40">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C55" t="s">
         <v>270</v>
@@ -13464,10 +13464,10 @@
     </row>
     <row r="56" spans="1:40">
       <c r="A56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C56" t="s">
         <v>270</v>
@@ -13583,10 +13583,10 @@
     </row>
     <row r="57" spans="1:40">
       <c r="A57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B57" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C57" t="s">
         <v>270</v>
@@ -13702,10 +13702,10 @@
     </row>
     <row r="58" spans="1:40">
       <c r="A58" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C58" t="s">
         <v>270</v>
@@ -13821,10 +13821,10 @@
     </row>
     <row r="59" spans="1:40">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B59" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C59" t="s">
         <v>270</v>
@@ -14062,10 +14062,10 @@
     </row>
     <row r="61" spans="1:40">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B61" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C61" t="s">
         <v>271</v>
@@ -14101,10 +14101,10 @@
         <v>46233</v>
       </c>
       <c r="N61" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O61" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -14178,10 +14178,10 @@
     </row>
     <row r="62" spans="1:40">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B62" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C62" t="s">
         <v>272</v>
@@ -14416,10 +14416,10 @@
     </row>
     <row r="64" spans="1:40">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C64" t="s">
         <v>273</v>
@@ -14651,10 +14651,10 @@
     </row>
     <row r="66" spans="1:40">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C66" t="s">
         <v>273</v>
@@ -14770,10 +14770,10 @@
     </row>
     <row r="67" spans="1:40">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C67" t="s">
         <v>273</v>
@@ -14928,10 +14928,10 @@
         <v>46245</v>
       </c>
       <c r="N68" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O68" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -15124,10 +15124,10 @@
     </row>
     <row r="70" spans="1:40">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B70" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C70" t="s">
         <v>274</v>
@@ -15243,10 +15243,10 @@
     </row>
     <row r="71" spans="1:40">
       <c r="A71" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" t="s">
         <v>274</v>
@@ -15362,10 +15362,10 @@
     </row>
     <row r="72" spans="1:40">
       <c r="A72" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C72" t="s">
         <v>274</v>
@@ -15481,10 +15481,10 @@
     </row>
     <row r="73" spans="1:40">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B73" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C73" t="s">
         <v>274</v>
@@ -15639,10 +15639,10 @@
         <v>46245</v>
       </c>
       <c r="N74" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O74" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -15832,10 +15832,10 @@
     </row>
     <row r="76" spans="1:40">
       <c r="A76" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B76" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C76" t="s">
         <v>274</v>
@@ -15990,10 +15990,10 @@
         <v>46245</v>
       </c>
       <c r="N77" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O77" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -16106,10 +16106,10 @@
         <v>46245</v>
       </c>
       <c r="N78" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O78" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -16454,10 +16454,10 @@
         <v>46245</v>
       </c>
       <c r="N81" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O81" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -16531,10 +16531,10 @@
     </row>
     <row r="82" spans="1:40">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C82" t="s">
         <v>274</v>
@@ -16689,10 +16689,10 @@
         <v>46245</v>
       </c>
       <c r="N83" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O83" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -17040,10 +17040,10 @@
         <v>46245</v>
       </c>
       <c r="N86" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O86" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -17117,10 +17117,10 @@
     </row>
     <row r="87" spans="1:40">
       <c r="A87" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="B87" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="C87" t="s">
         <v>274</v>
@@ -17156,19 +17156,19 @@
         <v>46245</v>
       </c>
       <c r="N87" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O87" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S87">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T87">
         <v>0</v>
@@ -17210,16 +17210,16 @@
         <v>5</v>
       </c>
       <c r="AG87">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AI87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ87" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AL87">
         <v>85</v>
@@ -17394,10 +17394,10 @@
         <v>46251</v>
       </c>
       <c r="N89" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O89" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q89">
         <v>0</v>
